--- a/docs/요구사항_정의서_v1.0_CKD.xlsx
+++ b/docs/요구사항_정의서_v1.0_CKD.xlsx
@@ -2083,8 +2083,8 @@
   <mergeCells count="4">
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2097,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="2"/>
@@ -2313,7 +2313,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I4" s="19" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>PR #9 — 6자리 코드 + 24h TTL + 미인증 403 차단</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
           <t>완료</t>
@@ -2524,7 +2528,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I8" s="19" t="n"/>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>5회 30분 잠금 + 테스트 5건 (2026-05-28 풀구현, memory 검증)</t>
+        </is>
+      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
           <t>완료</t>
@@ -3101,7 +3109,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I19" s="19" t="n"/>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>마이그12 — 운동(고/중강도)·좌식·결혼·가족력 3종 풀구현</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>완료</t>
@@ -3688,7 +3700,7 @@
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>Recharts + TanStack Query</t>
+          <t>7개 위젯 풀구현 (EgfrGauge·Risk·Egg·EgfrSim·Heatmap·Radial·Weekly)</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -3744,7 +3756,7 @@
       </c>
       <c r="I31" s="19" t="inlineStr">
         <is>
-          <t>의료법 및 의료광고법 준수</t>
+          <t>PR #6 — EgfrGauge·RiskGauge 우상단 배지 + 내부 옅은 워터마크</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -3798,7 +3810,7 @@
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>정직성 원칙 — 예상값 명시</t>
+          <t>PR #7 — What-if 시뮬레이션, 0~7일 일수 stepper 환산</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -4172,7 +4184,11 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I39" s="19" t="n"/>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>PR #12 — 5일 미체크인 슬럼프 감지 + 마이크로 챌린지 5종</t>
+        </is>
+      </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
           <t>완료</t>
@@ -5385,8 +5401,120 @@
       </c>
       <c r="K61" s="11" t="n"/>
     </row>
-    <row r="62" ht="84.75" customHeight="1" s="50"/>
-    <row r="63" ht="84.75" customHeight="1" s="50"/>
+    <row r="62" ht="84.75" customHeight="1" s="50">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>REQ-DASH-005</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>면책</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>임신 안전 안내</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>임신 체크 시 대시보드 상단에 산부인과 상담 권고·자가 식이/수분 제한 경고를 노출한다.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PR #6 medical-review 라벨</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="84.75" customHeight="1" s="50">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>REQ-AUTH-013</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>이메일 발송</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Gmail SMTP + demo fallback</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EMAIL_MODE=gmail 발송 옵션. 실제 메일 송신과 응답에 코드 노출(fallback)을 병행해 스팸 분류·지연을 대비한다.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PR #10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>풀스택</t>
+        </is>
+      </c>
+    </row>
     <row r="64" ht="84.75" customHeight="1" s="50"/>
     <row r="65" ht="84.75" customHeight="1" s="50"/>
     <row r="66" ht="84.75" customHeight="1" s="50"/>
